--- a/.planning/quick/quick-kayinleong-090/D2-Property-Data-Gaps.xlsx
+++ b/.planning/quick/quick-kayinleong-090/D2-Property-Data-Gaps.xlsx
@@ -156,7 +156,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -172,7 +177,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -568,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -653,182 +657,194 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Values or markers?</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>PRESENCE MARKERS ONLY — cells read 'on file' rather than showing the value, because no projects.export.json was present when this was built. To show real values, run scripts/export-projects-for-workbook.ts and rebuild.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>Caveat — read this</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Field VALUES are not reproduced here. The upstream report records presence/absence only (deliberately: no PII, no values), so a green cell means 'a value exists', not 'the value is correct'. Coverage is a snapshot as of quick-088; quick-089 has since changed some prices. Re-run scripts/data-completeness-report.ts for a fresh snapshot.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
-    </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Why blanks matter</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>The Finder refuses to invent data. A blank price renders as an em-dash to the agent, and a project with no bedrooms or size cannot be matched against a client brief. Every yellow cell is a question a D2 agent cannot answer at 11pm.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Sheets</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Property Details</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>The fill-in matrix — 87 projects. This is the sheet to send to the client.</t>
-        </is>
-      </c>
+          <t>Sheets</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Data Dictionary</t>
+          <t xml:space="preserve">  2. Property Details</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Every field on the project record: type, required, allowed values, meaning, who supplies it.</t>
+          <t>The fill-in matrix — 87 projects. This is the sheet to send to the client.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Gap Summary</t>
+          <t xml:space="preserve">  3. Data Dictionary</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>How many projects miss each field, worst first, with priority.</t>
+          <t>Every field on the project record: type, required, allowed values, meaning, who supplies it.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Unit Types</t>
+          <t xml:space="preserve">  4. Gap Summary</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Sub-record: the per-layout price/size table.</t>
+          <t>How many projects miss each field, worst first, with priority.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. Collateral</t>
+          <t xml:space="preserve">  5. Unit Types</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Sub-record: marketing assets (poster / video / fact sheet).</t>
+          <t>Sub-record: the per-layout price/size table.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7. Not Yet Captured</t>
+          <t xml:space="preserve">  6. Collateral</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Attributes D2 talks about that the system has NO field for at all — developer, maintenance fee, facilities, car parks and more. Decide per row whether to add a field or drop the attribute.</t>
+          <t>Sub-record: marketing assets (poster / video / fact sheet).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  7. Not Yet Captured</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Attributes D2 talks about that the system has NO field for at all — developer, maintenance fee, facilities, car parks and more. Decide per row whether to add a field or drop the attribute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  8. Data Traps</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Conventions that will corrupt the data if misread. Read before filling anything in.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Green 'on file'</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>A value is stored. Nothing needed.</t>
-        </is>
-      </c>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Yellow (blank)</t>
+          <t xml:space="preserve">  Green 'on file'</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>MISSING — please supply the value.</t>
+          <t>A value is stored. Nothing needed.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Peach (blank)</t>
+          <t xml:space="preserve">  Yellow (blank)</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>A value is stored but was never verified, and a wrong one is consequential. Please confirm.</t>
+          <t>MISSING — please supply the value.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Peach (blank)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>A value is stored but was never verified, and a wrong one is consequential. Please confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Grey 'n/a'</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>System-derived. Never filled in by hand.</t>
         </is>
@@ -1021,12 +1037,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1043,19 +1059,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O2" s="9" t="n"/>
-      <c r="P2" s="9" t="n"/>
-      <c r="Q2" s="9" t="n"/>
-      <c r="R2" s="10" t="n">
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="11" t="n">
         <v>1657</v>
       </c>
-      <c r="S2" s="10" t="n">
+      <c r="S2" s="11" t="n">
         <v>147</v>
       </c>
-      <c r="T2" s="10" t="n">
+      <c r="T2" s="11" t="n">
         <v>222</v>
       </c>
-      <c r="U2" s="10" t="inlineStr"/>
+      <c r="U2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1084,12 +1100,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1106,19 +1122,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O3" s="9" t="n"/>
-      <c r="P3" s="9" t="n"/>
-      <c r="Q3" s="9" t="n"/>
-      <c r="R3" s="10" t="n">
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="11" t="n">
         <v>1318</v>
       </c>
-      <c r="S3" s="10" t="n">
+      <c r="S3" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="T3" s="10" t="n">
+      <c r="T3" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="U3" s="10" t="inlineStr"/>
+      <c r="U3" s="11" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1151,12 +1167,12 @@
         </is>
       </c>
       <c r="H4" s="8" t="n"/>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1173,37 +1189,37 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O4" s="9" t="n"/>
-      <c r="P4" s="9" t="n"/>
-      <c r="Q4" s="9" t="n"/>
-      <c r="R4" s="10" t="n">
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="11" t="n">
         <v>5530</v>
       </c>
-      <c r="S4" s="10" t="n">
+      <c r="S4" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="T4" s="10" t="n">
+      <c r="T4" s="11" t="n">
         <v>92</v>
       </c>
-      <c r="U4" s="10" t="inlineStr"/>
+      <c r="U4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Aetas Damansara</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="13" t="n">
         <v>7</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -1211,13 +1227,13 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="14" t="n"/>
-      <c r="I5" s="14" t="n"/>
-      <c r="J5" s="14" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="14" t="n"/>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
+      <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
+      <c r="K5" s="15" t="n"/>
+      <c r="L5" s="15" t="n"/>
       <c r="M5" s="7" t="inlineStr">
         <is>
           <t>on file</t>
@@ -1231,16 +1247,16 @@
       <c r="O5" s="15" t="n"/>
       <c r="P5" s="15" t="n"/>
       <c r="Q5" s="15" t="n"/>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="S5" s="10" t="n">
+      <c r="S5" s="11" t="n">
         <v>534</v>
       </c>
-      <c r="T5" s="10" t="n">
+      <c r="T5" s="11" t="n">
         <v>613</v>
       </c>
-      <c r="U5" s="10" t="inlineStr"/>
+      <c r="U5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1277,12 +1293,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1303,19 +1319,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O6" s="9" t="n"/>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="9" t="n"/>
-      <c r="R6" s="10" t="n">
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="11" t="n">
         <v>1580</v>
       </c>
-      <c r="S6" s="10" t="n">
+      <c r="S6" s="11" t="n">
         <v>570</v>
       </c>
-      <c r="T6" s="10" t="n">
+      <c r="T6" s="11" t="n">
         <v>1044</v>
       </c>
-      <c r="U6" s="10" t="inlineStr"/>
+      <c r="U6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1340,12 +1356,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
       <c r="H7" s="8" t="n"/>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1362,19 +1378,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O7" s="9" t="n"/>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="9" t="n"/>
-      <c r="R7" s="10" t="n">
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="11" t="n">
         <v>1473</v>
       </c>
-      <c r="S7" s="10" t="n">
+      <c r="S7" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="T7" s="10" t="n">
+      <c r="T7" s="11" t="n">
         <v>125</v>
       </c>
-      <c r="U7" s="10" t="inlineStr"/>
+      <c r="U7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1403,12 +1419,12 @@
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n"/>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1429,19 +1445,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O8" s="9" t="n"/>
-      <c r="P8" s="9" t="n"/>
-      <c r="Q8" s="9" t="n"/>
-      <c r="R8" s="10" t="n">
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="11" t="n">
         <v>1019</v>
       </c>
-      <c r="S8" s="10" t="n">
+      <c r="S8" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="T8" s="10" t="n">
+      <c r="T8" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="U8" s="10" t="inlineStr"/>
+      <c r="U8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1470,12 +1486,12 @@
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
       <c r="H9" s="8" t="n"/>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1492,19 +1508,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O9" s="9" t="n"/>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="9" t="n"/>
-      <c r="R9" s="10" t="n">
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="11" t="n">
         <v>3362</v>
       </c>
-      <c r="S9" s="10" t="n">
+      <c r="S9" s="11" t="n">
         <v>517</v>
       </c>
-      <c r="T9" s="10" t="n">
+      <c r="T9" s="11" t="n">
         <v>347</v>
       </c>
-      <c r="U9" s="10" t="inlineStr"/>
+      <c r="U9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1533,12 +1549,12 @@
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="n"/>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1555,19 +1571,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O10" s="9" t="n"/>
-      <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="9" t="n"/>
-      <c r="R10" s="10" t="n">
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="10" t="n"/>
+      <c r="R10" s="11" t="n">
         <v>796</v>
       </c>
-      <c r="S10" s="10" t="n">
+      <c r="S10" s="11" t="n">
         <v>170</v>
       </c>
-      <c r="T10" s="10" t="n">
+      <c r="T10" s="11" t="n">
         <v>140</v>
       </c>
-      <c r="U10" s="10" t="inlineStr"/>
+      <c r="U10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1600,12 +1616,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1626,19 +1642,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O11" s="9" t="n"/>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="9" t="n"/>
-      <c r="R11" s="10" t="n">
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="11" t="n">
         <v>2294</v>
       </c>
-      <c r="S11" s="10" t="n">
+      <c r="S11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="T11" s="10" t="n">
+      <c r="T11" s="11" t="n">
         <v>197</v>
       </c>
-      <c r="U11" s="10" t="inlineStr"/>
+      <c r="U11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1671,12 +1687,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1697,19 +1713,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O12" s="9" t="n"/>
-      <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="9" t="n"/>
-      <c r="R12" s="10" t="n">
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n"/>
+      <c r="R12" s="11" t="n">
         <v>5051</v>
       </c>
-      <c r="S12" s="10" t="n">
+      <c r="S12" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="T12" s="10" t="n">
+      <c r="T12" s="11" t="n">
         <v>74</v>
       </c>
-      <c r="U12" s="10" t="inlineStr"/>
+      <c r="U12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1746,12 +1762,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1772,19 +1788,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O13" s="9" t="n"/>
-      <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="9" t="n"/>
-      <c r="R13" s="10" t="n">
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="11" t="n">
         <v>1446</v>
       </c>
-      <c r="S13" s="10" t="n">
+      <c r="S13" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="T13" s="10" t="n">
+      <c r="T13" s="11" t="n">
         <v>326</v>
       </c>
-      <c r="U13" s="10" t="inlineStr"/>
+      <c r="U13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1821,12 +1837,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1851,19 +1867,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O14" s="9" t="n"/>
-      <c r="P14" s="9" t="n"/>
-      <c r="Q14" s="9" t="n"/>
-      <c r="R14" s="10" t="n">
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="11" t="n">
         <v>1196</v>
       </c>
-      <c r="S14" s="10" t="n">
+      <c r="S14" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="T14" s="10" t="n">
+      <c r="T14" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="U14" s="10" t="inlineStr"/>
+      <c r="U14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1900,12 +1916,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1926,19 +1942,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O15" s="9" t="n"/>
-      <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="9" t="n"/>
-      <c r="R15" s="10" t="n">
+      <c r="O15" s="10" t="n"/>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="11" t="n">
         <v>5359</v>
       </c>
-      <c r="S15" s="10" t="n">
+      <c r="S15" s="11" t="n">
         <v>660</v>
       </c>
-      <c r="T15" s="10" t="n">
+      <c r="T15" s="11" t="n">
         <v>1152</v>
       </c>
-      <c r="U15" s="10" t="inlineStr"/>
+      <c r="U15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1971,12 +1987,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -1993,19 +2009,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O16" s="9" t="n"/>
-      <c r="P16" s="9" t="n"/>
-      <c r="Q16" s="9" t="n"/>
-      <c r="R16" s="10" t="n">
+      <c r="O16" s="10" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n"/>
+      <c r="R16" s="11" t="n">
         <v>2319</v>
       </c>
-      <c r="S16" s="10" t="n">
+      <c r="S16" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="T16" s="10" t="n">
+      <c r="T16" s="11" t="n">
         <v>86</v>
       </c>
-      <c r="U16" s="10" t="inlineStr"/>
+      <c r="U16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2042,12 +2058,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2068,19 +2084,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O17" s="9" t="n"/>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="9" t="n"/>
-      <c r="R17" s="10" t="n">
+      <c r="O17" s="10" t="n"/>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="10" t="n"/>
+      <c r="R17" s="11" t="n">
         <v>3005</v>
       </c>
-      <c r="S17" s="10" t="n">
+      <c r="S17" s="11" t="n">
         <v>1060</v>
       </c>
-      <c r="T17" s="10" t="n">
+      <c r="T17" s="11" t="n">
         <v>1915</v>
       </c>
-      <c r="U17" s="10" t="inlineStr"/>
+      <c r="U17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2117,12 +2133,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2147,19 +2163,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O18" s="9" t="n"/>
-      <c r="P18" s="9" t="n"/>
-      <c r="Q18" s="9" t="n"/>
-      <c r="R18" s="10" t="n">
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="10" t="n"/>
+      <c r="R18" s="11" t="n">
         <v>2333</v>
       </c>
-      <c r="S18" s="10" t="n">
+      <c r="S18" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="T18" s="10" t="n">
+      <c r="T18" s="11" t="n">
         <v>455</v>
       </c>
-      <c r="U18" s="10" t="inlineStr"/>
+      <c r="U18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2196,12 +2212,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2226,19 +2242,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O19" s="9" t="n"/>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="10" t="n">
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="11" t="n">
         <v>1236</v>
       </c>
-      <c r="S19" s="10" t="n">
+      <c r="S19" s="11" t="n">
         <v>732</v>
       </c>
-      <c r="T19" s="10" t="n">
+      <c r="T19" s="11" t="n">
         <v>736</v>
       </c>
-      <c r="U19" s="10" t="inlineStr"/>
+      <c r="U19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2271,12 +2287,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2301,19 +2317,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O20" s="9" t="n"/>
-      <c r="P20" s="9" t="n"/>
-      <c r="Q20" s="9" t="n"/>
-      <c r="R20" s="10" t="n">
+      <c r="O20" s="10" t="n"/>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="10" t="n"/>
+      <c r="R20" s="11" t="n">
         <v>2167</v>
       </c>
-      <c r="S20" s="10" t="n">
+      <c r="S20" s="11" t="n">
         <v>343</v>
       </c>
-      <c r="T20" s="10" t="n">
+      <c r="T20" s="11" t="n">
         <v>2550</v>
       </c>
-      <c r="U20" s="10" t="inlineStr"/>
+      <c r="U20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2350,12 +2366,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2376,19 +2392,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O21" s="9" t="n"/>
-      <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="9" t="n"/>
-      <c r="R21" s="10" t="n">
+      <c r="O21" s="10" t="n"/>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="10" t="n"/>
+      <c r="R21" s="11" t="n">
         <v>2778</v>
       </c>
-      <c r="S21" s="10" t="n">
+      <c r="S21" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="T21" s="10" t="n">
+      <c r="T21" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="U21" s="10" t="inlineStr"/>
+      <c r="U21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2425,12 +2441,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2451,19 +2467,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O22" s="9" t="n"/>
-      <c r="P22" s="9" t="n"/>
-      <c r="Q22" s="9" t="n"/>
-      <c r="R22" s="10" t="n">
+      <c r="O22" s="10" t="n"/>
+      <c r="P22" s="10" t="n"/>
+      <c r="Q22" s="10" t="n"/>
+      <c r="R22" s="11" t="n">
         <v>3208</v>
       </c>
-      <c r="S22" s="10" t="n">
+      <c r="S22" s="11" t="n">
         <v>71</v>
       </c>
-      <c r="T22" s="10" t="n">
+      <c r="T22" s="11" t="n">
         <v>89</v>
       </c>
-      <c r="U22" s="10" t="inlineStr"/>
+      <c r="U22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2496,12 +2512,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2518,19 +2534,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O23" s="9" t="n"/>
-      <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="9" t="n"/>
-      <c r="R23" s="10" t="n">
+      <c r="O23" s="10" t="n"/>
+      <c r="P23" s="10" t="n"/>
+      <c r="Q23" s="10" t="n"/>
+      <c r="R23" s="11" t="n">
         <v>2086</v>
       </c>
-      <c r="S23" s="10" t="n">
+      <c r="S23" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="T23" s="10" t="n">
+      <c r="T23" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="U23" s="10" t="inlineStr"/>
+      <c r="U23" s="11" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2567,12 +2583,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2597,19 +2613,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O24" s="9" t="n"/>
-      <c r="P24" s="9" t="n"/>
-      <c r="Q24" s="9" t="n"/>
-      <c r="R24" s="10" t="n">
+      <c r="O24" s="10" t="n"/>
+      <c r="P24" s="10" t="n"/>
+      <c r="Q24" s="10" t="n"/>
+      <c r="R24" s="11" t="n">
         <v>2529</v>
       </c>
-      <c r="S24" s="10" t="n">
+      <c r="S24" s="11" t="n">
         <v>411</v>
       </c>
-      <c r="T24" s="10" t="n">
+      <c r="T24" s="11" t="n">
         <v>687</v>
       </c>
-      <c r="U24" s="10" t="inlineStr"/>
+      <c r="U24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2642,12 +2658,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2664,19 +2680,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O25" s="9" t="n"/>
-      <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="9" t="n"/>
-      <c r="R25" s="10" t="n">
+      <c r="O25" s="10" t="n"/>
+      <c r="P25" s="10" t="n"/>
+      <c r="Q25" s="10" t="n"/>
+      <c r="R25" s="11" t="n">
         <v>2660</v>
       </c>
-      <c r="S25" s="10" t="n">
+      <c r="S25" s="11" t="n">
         <v>58</v>
       </c>
-      <c r="T25" s="10" t="n">
+      <c r="T25" s="11" t="n">
         <v>294</v>
       </c>
-      <c r="U25" s="10" t="inlineStr"/>
+      <c r="U25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2709,12 +2725,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2735,19 +2751,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O26" s="9" t="n"/>
-      <c r="P26" s="9" t="n"/>
-      <c r="Q26" s="9" t="n"/>
-      <c r="R26" s="10" t="n">
+      <c r="O26" s="10" t="n"/>
+      <c r="P26" s="10" t="n"/>
+      <c r="Q26" s="10" t="n"/>
+      <c r="R26" s="11" t="n">
         <v>3179</v>
       </c>
-      <c r="S26" s="10" t="n">
+      <c r="S26" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="T26" s="10" t="n">
+      <c r="T26" s="11" t="n">
         <v>188</v>
       </c>
-      <c r="U26" s="10" t="inlineStr"/>
+      <c r="U26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2772,12 +2788,12 @@
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2794,19 +2810,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O27" s="9" t="n"/>
-      <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="9" t="n"/>
-      <c r="R27" s="10" t="n">
+      <c r="O27" s="10" t="n"/>
+      <c r="P27" s="10" t="n"/>
+      <c r="Q27" s="10" t="n"/>
+      <c r="R27" s="11" t="n">
         <v>1926</v>
       </c>
-      <c r="S27" s="10" t="n">
+      <c r="S27" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="T27" s="10" t="n">
+      <c r="T27" s="11" t="n">
         <v>646</v>
       </c>
-      <c r="U27" s="10" t="inlineStr"/>
+      <c r="U27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2843,12 +2859,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2869,19 +2885,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O28" s="9" t="n"/>
-      <c r="P28" s="9" t="n"/>
-      <c r="Q28" s="9" t="n"/>
-      <c r="R28" s="10" t="n">
+      <c r="O28" s="10" t="n"/>
+      <c r="P28" s="10" t="n"/>
+      <c r="Q28" s="10" t="n"/>
+      <c r="R28" s="11" t="n">
         <v>6093</v>
       </c>
-      <c r="S28" s="10" t="n">
+      <c r="S28" s="11" t="n">
         <v>146</v>
       </c>
-      <c r="T28" s="10" t="n">
+      <c r="T28" s="11" t="n">
         <v>587</v>
       </c>
-      <c r="U28" s="10" t="inlineStr"/>
+      <c r="U28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -2914,12 +2930,12 @@
         </is>
       </c>
       <c r="H29" s="8" t="n"/>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -2936,19 +2952,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O29" s="9" t="n"/>
-      <c r="P29" s="9" t="n"/>
-      <c r="Q29" s="9" t="n"/>
-      <c r="R29" s="10" t="n">
+      <c r="O29" s="10" t="n"/>
+      <c r="P29" s="10" t="n"/>
+      <c r="Q29" s="10" t="n"/>
+      <c r="R29" s="11" t="n">
         <v>1592</v>
       </c>
-      <c r="S29" s="10" t="n">
+      <c r="S29" s="11" t="n">
         <v>303</v>
       </c>
-      <c r="T29" s="10" t="n">
+      <c r="T29" s="11" t="n">
         <v>230</v>
       </c>
-      <c r="U29" s="10" t="inlineStr"/>
+      <c r="U29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2985,12 +3001,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3011,19 +3027,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O30" s="9" t="n"/>
-      <c r="P30" s="9" t="n"/>
-      <c r="Q30" s="9" t="n"/>
-      <c r="R30" s="10" t="n">
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="10" t="n"/>
+      <c r="Q30" s="10" t="n"/>
+      <c r="R30" s="11" t="n">
         <v>1403</v>
       </c>
-      <c r="S30" s="10" t="n">
+      <c r="S30" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="T30" s="10" t="n">
+      <c r="T30" s="11" t="n">
         <v>146</v>
       </c>
-      <c r="U30" s="10" t="inlineStr"/>
+      <c r="U30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3060,12 +3076,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3086,19 +3102,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O31" s="9" t="n"/>
-      <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="10" t="n">
+      <c r="O31" s="10" t="n"/>
+      <c r="P31" s="10" t="n"/>
+      <c r="Q31" s="10" t="n"/>
+      <c r="R31" s="11" t="n">
         <v>3028</v>
       </c>
-      <c r="S31" s="10" t="n">
+      <c r="S31" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="T31" s="10" t="n">
+      <c r="T31" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="U31" s="10" t="inlineStr"/>
+      <c r="U31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3135,12 +3151,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3161,19 +3177,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O32" s="9" t="n"/>
-      <c r="P32" s="9" t="n"/>
-      <c r="Q32" s="9" t="n"/>
-      <c r="R32" s="10" t="n">
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="11" t="n">
         <v>1567</v>
       </c>
-      <c r="S32" s="10" t="n">
+      <c r="S32" s="11" t="n">
         <v>102</v>
       </c>
-      <c r="T32" s="10" t="n">
+      <c r="T32" s="11" t="n">
         <v>105</v>
       </c>
-      <c r="U32" s="10" t="inlineStr"/>
+      <c r="U32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3210,12 +3226,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3236,19 +3252,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O33" s="9" t="n"/>
-      <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="9" t="n"/>
-      <c r="R33" s="10" t="n">
+      <c r="O33" s="10" t="n"/>
+      <c r="P33" s="10" t="n"/>
+      <c r="Q33" s="10" t="n"/>
+      <c r="R33" s="11" t="n">
         <v>2827</v>
       </c>
-      <c r="S33" s="10" t="n">
+      <c r="S33" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="T33" s="10" t="n">
+      <c r="T33" s="11" t="n">
         <v>102</v>
       </c>
-      <c r="U33" s="10" t="inlineStr"/>
+      <c r="U33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3285,12 +3301,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3311,19 +3327,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O34" s="9" t="n"/>
-      <c r="P34" s="9" t="n"/>
-      <c r="Q34" s="9" t="n"/>
-      <c r="R34" s="10" t="n">
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="10" t="n"/>
+      <c r="Q34" s="10" t="n"/>
+      <c r="R34" s="11" t="n">
         <v>6072</v>
       </c>
-      <c r="S34" s="10" t="n">
+      <c r="S34" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="T34" s="10" t="n">
+      <c r="T34" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="U34" s="10" t="inlineStr"/>
+      <c r="U34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3360,12 +3376,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3386,19 +3402,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O35" s="9" t="n"/>
-      <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="10" t="n">
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="10" t="n"/>
+      <c r="Q35" s="10" t="n"/>
+      <c r="R35" s="11" t="n">
         <v>5411</v>
       </c>
-      <c r="S35" s="10" t="n">
+      <c r="S35" s="11" t="n">
         <v>185</v>
       </c>
-      <c r="T35" s="10" t="n">
+      <c r="T35" s="11" t="n">
         <v>478</v>
       </c>
-      <c r="U35" s="10" t="inlineStr"/>
+      <c r="U35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -3435,12 +3451,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3461,19 +3477,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O36" s="9" t="n"/>
-      <c r="P36" s="9" t="n"/>
-      <c r="Q36" s="9" t="n"/>
-      <c r="R36" s="10" t="n">
+      <c r="O36" s="10" t="n"/>
+      <c r="P36" s="10" t="n"/>
+      <c r="Q36" s="10" t="n"/>
+      <c r="R36" s="11" t="n">
         <v>2946</v>
       </c>
-      <c r="S36" s="10" t="n">
+      <c r="S36" s="11" t="n">
         <v>107</v>
       </c>
-      <c r="T36" s="10" t="n">
+      <c r="T36" s="11" t="n">
         <v>441</v>
       </c>
-      <c r="U36" s="10" t="inlineStr"/>
+      <c r="U36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3502,12 +3518,12 @@
         </is>
       </c>
       <c r="H37" s="8" t="n"/>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3524,19 +3540,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O37" s="9" t="n"/>
-      <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="9" t="n"/>
-      <c r="R37" s="10" t="n">
+      <c r="O37" s="10" t="n"/>
+      <c r="P37" s="10" t="n"/>
+      <c r="Q37" s="10" t="n"/>
+      <c r="R37" s="11" t="n">
         <v>889</v>
       </c>
-      <c r="S37" s="10" t="n">
+      <c r="S37" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="T37" s="10" t="n">
+      <c r="T37" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="U37" s="10" t="inlineStr"/>
+      <c r="U37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -3573,12 +3589,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3599,19 +3615,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O38" s="9" t="n"/>
-      <c r="P38" s="9" t="n"/>
-      <c r="Q38" s="9" t="n"/>
-      <c r="R38" s="10" t="n">
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="11" t="n">
         <v>2150</v>
       </c>
-      <c r="S38" s="10" t="n">
+      <c r="S38" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="T38" s="10" t="n">
+      <c r="T38" s="11" t="n">
         <v>170</v>
       </c>
-      <c r="U38" s="10" t="inlineStr"/>
+      <c r="U38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3648,12 +3664,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3674,19 +3690,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O39" s="9" t="n"/>
-      <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="9" t="n"/>
-      <c r="R39" s="10" t="n">
+      <c r="O39" s="10" t="n"/>
+      <c r="P39" s="10" t="n"/>
+      <c r="Q39" s="10" t="n"/>
+      <c r="R39" s="11" t="n">
         <v>2343</v>
       </c>
-      <c r="S39" s="10" t="n">
+      <c r="S39" s="11" t="n">
         <v>362</v>
       </c>
-      <c r="T39" s="10" t="n">
+      <c r="T39" s="11" t="n">
         <v>275</v>
       </c>
-      <c r="U39" s="10" t="inlineStr"/>
+      <c r="U39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -3723,12 +3739,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3749,19 +3765,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O40" s="9" t="n"/>
-      <c r="P40" s="9" t="n"/>
-      <c r="Q40" s="9" t="n"/>
-      <c r="R40" s="10" t="n">
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="10" t="n"/>
+      <c r="Q40" s="10" t="n"/>
+      <c r="R40" s="11" t="n">
         <v>3240</v>
       </c>
-      <c r="S40" s="10" t="n">
+      <c r="S40" s="11" t="n">
         <v>287</v>
       </c>
-      <c r="T40" s="10" t="n">
+      <c r="T40" s="11" t="n">
         <v>446</v>
       </c>
-      <c r="U40" s="10" t="inlineStr"/>
+      <c r="U40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -3798,12 +3814,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3828,19 +3844,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O41" s="9" t="n"/>
-      <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="9" t="n"/>
-      <c r="R41" s="10" t="n">
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="10" t="n"/>
+      <c r="Q41" s="10" t="n"/>
+      <c r="R41" s="11" t="n">
         <v>3662</v>
       </c>
-      <c r="S41" s="10" t="n">
+      <c r="S41" s="11" t="n">
         <v>162</v>
       </c>
-      <c r="T41" s="10" t="n">
+      <c r="T41" s="11" t="n">
         <v>717</v>
       </c>
-      <c r="U41" s="10" t="inlineStr"/>
+      <c r="U41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3877,12 +3893,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -3903,37 +3919,37 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O42" s="9" t="n"/>
-      <c r="P42" s="9" t="n"/>
-      <c r="Q42" s="9" t="n"/>
-      <c r="R42" s="10" t="n">
+      <c r="O42" s="10" t="n"/>
+      <c r="P42" s="10" t="n"/>
+      <c r="Q42" s="10" t="n"/>
+      <c r="R42" s="11" t="n">
         <v>2331</v>
       </c>
-      <c r="S42" s="10" t="n">
+      <c r="S42" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="T42" s="10" t="n">
+      <c r="T42" s="11" t="n">
         <v>752</v>
       </c>
-      <c r="U42" s="10" t="inlineStr"/>
+      <c r="U42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Papyrus North Kiara</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="D43" s="13" t="n">
         <v>7</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -3941,13 +3957,13 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="F43" s="14" t="n"/>
-      <c r="G43" s="14" t="n"/>
-      <c r="H43" s="14" t="n"/>
-      <c r="I43" s="14" t="n"/>
-      <c r="J43" s="14" t="n"/>
-      <c r="K43" s="14" t="n"/>
-      <c r="L43" s="14" t="n"/>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="15" t="n"/>
+      <c r="H43" s="15" t="n"/>
+      <c r="I43" s="15" t="n"/>
+      <c r="J43" s="15" t="n"/>
+      <c r="K43" s="15" t="n"/>
+      <c r="L43" s="15" t="n"/>
       <c r="M43" s="7" t="inlineStr">
         <is>
           <t>on file</t>
@@ -3961,16 +3977,16 @@
       <c r="O43" s="15" t="n"/>
       <c r="P43" s="15" t="n"/>
       <c r="Q43" s="15" t="n"/>
-      <c r="R43" s="10" t="n">
+      <c r="R43" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="S43" s="10" t="n">
+      <c r="S43" s="11" t="n">
         <v>157</v>
       </c>
-      <c r="T43" s="10" t="n">
+      <c r="T43" s="11" t="n">
         <v>161</v>
       </c>
-      <c r="U43" s="10" t="inlineStr"/>
+      <c r="U43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4007,12 +4023,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4033,19 +4049,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O44" s="9" t="n"/>
-      <c r="P44" s="9" t="n"/>
-      <c r="Q44" s="9" t="n"/>
-      <c r="R44" s="10" t="n">
+      <c r="O44" s="10" t="n"/>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n"/>
+      <c r="R44" s="11" t="n">
         <v>2058</v>
       </c>
-      <c r="S44" s="10" t="n">
+      <c r="S44" s="11" t="n">
         <v>54</v>
       </c>
-      <c r="T44" s="10" t="n">
+      <c r="T44" s="11" t="n">
         <v>148</v>
       </c>
-      <c r="U44" s="10" t="inlineStr"/>
+      <c r="U44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4082,12 +4098,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4108,19 +4124,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O45" s="9" t="n"/>
-      <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="9" t="n"/>
-      <c r="R45" s="10" t="n">
+      <c r="O45" s="10" t="n"/>
+      <c r="P45" s="10" t="n"/>
+      <c r="Q45" s="10" t="n"/>
+      <c r="R45" s="11" t="n">
         <v>4913</v>
       </c>
-      <c r="S45" s="10" t="n">
+      <c r="S45" s="11" t="n">
         <v>317</v>
       </c>
-      <c r="T45" s="10" t="n">
+      <c r="T45" s="11" t="n">
         <v>555</v>
       </c>
-      <c r="U45" s="10" t="inlineStr"/>
+      <c r="U45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4153,12 +4169,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4179,16 +4195,16 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O46" s="9" t="n"/>
-      <c r="P46" s="9" t="n"/>
-      <c r="Q46" s="9" t="n"/>
-      <c r="R46" s="10" t="n">
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="10" t="n"/>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="11" t="n">
         <v>1680</v>
       </c>
-      <c r="S46" s="10" t="n">
+      <c r="S46" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="T46" s="10" t="n">
+      <c r="T46" s="11" t="n">
         <v>301</v>
       </c>
       <c r="U46" s="8" t="inlineStr">
@@ -4232,12 +4248,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4258,16 +4274,16 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O47" s="9" t="n"/>
-      <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="9" t="n"/>
-      <c r="R47" s="10" t="n">
+      <c r="O47" s="10" t="n"/>
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="11" t="n">
         <v>1513</v>
       </c>
-      <c r="S47" s="10" t="n">
+      <c r="S47" s="11" t="n">
         <v>106</v>
       </c>
-      <c r="T47" s="10" t="n">
+      <c r="T47" s="11" t="n">
         <v>219</v>
       </c>
       <c r="U47" s="8" t="inlineStr">
@@ -4311,12 +4327,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr">
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4337,19 +4353,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O48" s="9" t="n"/>
-      <c r="P48" s="9" t="n"/>
-      <c r="Q48" s="9" t="n"/>
-      <c r="R48" s="10" t="n">
+      <c r="O48" s="10" t="n"/>
+      <c r="P48" s="10" t="n"/>
+      <c r="Q48" s="10" t="n"/>
+      <c r="R48" s="11" t="n">
         <v>2827</v>
       </c>
-      <c r="S48" s="10" t="n">
+      <c r="S48" s="11" t="n">
         <v>290</v>
       </c>
-      <c r="T48" s="10" t="n">
+      <c r="T48" s="11" t="n">
         <v>345</v>
       </c>
-      <c r="U48" s="10" t="inlineStr"/>
+      <c r="U48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4386,12 +4402,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4416,19 +4432,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O49" s="9" t="n"/>
-      <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="9" t="n"/>
-      <c r="R49" s="10" t="n">
+      <c r="O49" s="10" t="n"/>
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="11" t="n">
         <v>3130</v>
       </c>
-      <c r="S49" s="10" t="n">
+      <c r="S49" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="T49" s="10" t="n">
+      <c r="T49" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="U49" s="10" t="inlineStr"/>
+      <c r="U49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4461,12 +4477,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4487,37 +4503,37 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O50" s="9" t="n"/>
-      <c r="P50" s="9" t="n"/>
-      <c r="Q50" s="9" t="n"/>
-      <c r="R50" s="10" t="n">
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="11" t="n">
         <v>1951</v>
       </c>
-      <c r="S50" s="10" t="n">
+      <c r="S50" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="T50" s="10" t="n">
+      <c r="T50" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="U50" s="10" t="inlineStr"/>
+      <c r="U50" s="11" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>Property 1</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D51" s="13" t="n">
         <v>3</v>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -4525,7 +4541,7 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="F51" s="14" t="n"/>
+      <c r="F51" s="15" t="n"/>
       <c r="G51" s="7" t="inlineStr">
         <is>
           <t>on file</t>
@@ -4536,12 +4552,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4551,23 +4567,23 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="L51" s="14" t="n"/>
+      <c r="L51" s="15" t="n"/>
       <c r="M51" s="7" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
       </c>
-      <c r="N51" s="14" t="n"/>
+      <c r="N51" s="15" t="n"/>
       <c r="O51" s="15" t="n"/>
       <c r="P51" s="15" t="n"/>
       <c r="Q51" s="15" t="n"/>
-      <c r="R51" s="10" t="n">
+      <c r="R51" s="11" t="n">
         <v>1351</v>
       </c>
-      <c r="S51" s="10" t="n">
+      <c r="S51" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="T51" s="10" t="n">
+      <c r="T51" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U51" s="8" t="inlineStr">
@@ -4607,12 +4623,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="inlineStr">
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4633,19 +4649,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O52" s="9" t="n"/>
-      <c r="P52" s="9" t="n"/>
-      <c r="Q52" s="9" t="n"/>
-      <c r="R52" s="10" t="n">
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="10" t="n"/>
+      <c r="Q52" s="10" t="n"/>
+      <c r="R52" s="11" t="n">
         <v>3151</v>
       </c>
-      <c r="S52" s="10" t="n">
+      <c r="S52" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="T52" s="10" t="n">
+      <c r="T52" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="U52" s="10" t="inlineStr"/>
+      <c r="U52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -4682,12 +4698,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr">
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4708,19 +4724,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O53" s="9" t="n"/>
-      <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="9" t="n"/>
-      <c r="R53" s="10" t="n">
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="10" t="n"/>
+      <c r="Q53" s="10" t="n"/>
+      <c r="R53" s="11" t="n">
         <v>3802</v>
       </c>
-      <c r="S53" s="10" t="n">
+      <c r="S53" s="11" t="n">
         <v>73</v>
       </c>
-      <c r="T53" s="10" t="n">
+      <c r="T53" s="11" t="n">
         <v>122</v>
       </c>
-      <c r="U53" s="10" t="inlineStr"/>
+      <c r="U53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -4753,12 +4769,12 @@
         </is>
       </c>
       <c r="H54" s="8" t="n"/>
-      <c r="I54" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr">
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4783,19 +4799,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O54" s="9" t="n"/>
-      <c r="P54" s="9" t="n"/>
-      <c r="Q54" s="9" t="n"/>
-      <c r="R54" s="10" t="n">
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="11" t="n">
         <v>1795</v>
       </c>
-      <c r="S54" s="10" t="n">
+      <c r="S54" s="11" t="n">
         <v>377</v>
       </c>
-      <c r="T54" s="10" t="n">
+      <c r="T54" s="11" t="n">
         <v>428</v>
       </c>
-      <c r="U54" s="10" t="inlineStr"/>
+      <c r="U54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -4828,12 +4844,12 @@
         </is>
       </c>
       <c r="H55" s="8" t="n"/>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4854,16 +4870,16 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O55" s="9" t="n"/>
-      <c r="P55" s="9" t="n"/>
-      <c r="Q55" s="9" t="n"/>
-      <c r="R55" s="10" t="n">
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="11" t="n">
         <v>3534</v>
       </c>
-      <c r="S55" s="10" t="n">
+      <c r="S55" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="T55" s="10" t="n">
+      <c r="T55" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U55" s="8" t="inlineStr">
@@ -4907,12 +4923,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="inlineStr">
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -4937,19 +4953,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O56" s="9" t="n"/>
-      <c r="P56" s="9" t="n"/>
-      <c r="Q56" s="9" t="n"/>
-      <c r="R56" s="10" t="n">
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="10" t="n"/>
+      <c r="Q56" s="10" t="n"/>
+      <c r="R56" s="11" t="n">
         <v>2952</v>
       </c>
-      <c r="S56" s="10" t="n">
+      <c r="S56" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="T56" s="10" t="n">
+      <c r="T56" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="U56" s="10" t="inlineStr"/>
+      <c r="U56" s="11" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -4982,12 +4998,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr">
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5008,19 +5024,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O57" s="9" t="n"/>
-      <c r="P57" s="9" t="n"/>
-      <c r="Q57" s="9" t="n"/>
-      <c r="R57" s="10" t="n">
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="11" t="n">
         <v>1012</v>
       </c>
-      <c r="S57" s="10" t="n">
+      <c r="S57" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="T57" s="10" t="n">
+      <c r="T57" s="11" t="n">
         <v>115</v>
       </c>
-      <c r="U57" s="10" t="inlineStr"/>
+      <c r="U57" s="11" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -5057,12 +5073,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="inlineStr">
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5083,19 +5099,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O58" s="9" t="n"/>
-      <c r="P58" s="9" t="n"/>
-      <c r="Q58" s="9" t="n"/>
-      <c r="R58" s="10" t="n">
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="11" t="n">
         <v>1673</v>
       </c>
-      <c r="S58" s="10" t="n">
+      <c r="S58" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="T58" s="10" t="n">
+      <c r="T58" s="11" t="n">
         <v>147</v>
       </c>
-      <c r="U58" s="10" t="inlineStr"/>
+      <c r="U58" s="11" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -5128,12 +5144,12 @@
         </is>
       </c>
       <c r="H59" s="8" t="n"/>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr">
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5154,19 +5170,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O59" s="9" t="n"/>
-      <c r="P59" s="9" t="n"/>
-      <c r="Q59" s="9" t="n"/>
-      <c r="R59" s="10" t="n">
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="10" t="n"/>
+      <c r="Q59" s="10" t="n"/>
+      <c r="R59" s="11" t="n">
         <v>2103</v>
       </c>
-      <c r="S59" s="10" t="n">
+      <c r="S59" s="11" t="n">
         <v>81</v>
       </c>
-      <c r="T59" s="10" t="n">
+      <c r="T59" s="11" t="n">
         <v>171</v>
       </c>
-      <c r="U59" s="10" t="inlineStr"/>
+      <c r="U59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -5203,12 +5219,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr">
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5229,19 +5245,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O60" s="9" t="n"/>
-      <c r="P60" s="9" t="n"/>
-      <c r="Q60" s="9" t="n"/>
-      <c r="R60" s="10" t="n">
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="11" t="n">
         <v>6855</v>
       </c>
-      <c r="S60" s="10" t="n">
+      <c r="S60" s="11" t="n">
         <v>103</v>
       </c>
-      <c r="T60" s="10" t="n">
+      <c r="T60" s="11" t="n">
         <v>256</v>
       </c>
-      <c r="U60" s="10" t="inlineStr"/>
+      <c r="U60" s="11" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -5278,12 +5294,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5304,19 +5320,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O61" s="9" t="n"/>
-      <c r="P61" s="9" t="n"/>
-      <c r="Q61" s="9" t="n"/>
-      <c r="R61" s="10" t="n">
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="11" t="n">
         <v>1981</v>
       </c>
-      <c r="S61" s="10" t="n">
+      <c r="S61" s="11" t="n">
         <v>106</v>
       </c>
-      <c r="T61" s="10" t="n">
+      <c r="T61" s="11" t="n">
         <v>255</v>
       </c>
-      <c r="U61" s="10" t="inlineStr"/>
+      <c r="U61" s="11" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5349,12 +5365,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr">
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5371,19 +5387,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O62" s="9" t="n"/>
-      <c r="P62" s="9" t="n"/>
-      <c r="Q62" s="9" t="n"/>
-      <c r="R62" s="10" t="n">
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="10" t="n"/>
+      <c r="Q62" s="10" t="n"/>
+      <c r="R62" s="11" t="n">
         <v>3694</v>
       </c>
-      <c r="S62" s="10" t="n">
+      <c r="S62" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="T62" s="10" t="n">
+      <c r="T62" s="11" t="n">
         <v>202</v>
       </c>
-      <c r="U62" s="10" t="inlineStr"/>
+      <c r="U62" s="11" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5420,12 +5436,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J63" s="7" t="inlineStr">
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5450,19 +5466,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O63" s="9" t="n"/>
-      <c r="P63" s="9" t="n"/>
-      <c r="Q63" s="9" t="n"/>
-      <c r="R63" s="10" t="n">
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="11" t="n">
         <v>1837</v>
       </c>
-      <c r="S63" s="10" t="n">
+      <c r="S63" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="T63" s="10" t="n">
+      <c r="T63" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="U63" s="10" t="inlineStr"/>
+      <c r="U63" s="11" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5491,12 +5507,12 @@
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J64" s="7" t="inlineStr">
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5513,16 +5529,16 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O64" s="9" t="n"/>
-      <c r="P64" s="9" t="n"/>
-      <c r="Q64" s="9" t="n"/>
-      <c r="R64" s="10" t="n">
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="11" t="n">
         <v>1449</v>
       </c>
-      <c r="S64" s="10" t="n">
+      <c r="S64" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="T64" s="10" t="n">
+      <c r="T64" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U64" s="8" t="inlineStr">
@@ -5566,12 +5582,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J65" s="7" t="inlineStr">
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5592,19 +5608,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O65" s="9" t="n"/>
-      <c r="P65" s="9" t="n"/>
-      <c r="Q65" s="9" t="n"/>
-      <c r="R65" s="10" t="n">
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="10" t="n"/>
+      <c r="Q65" s="10" t="n"/>
+      <c r="R65" s="11" t="n">
         <v>3202</v>
       </c>
-      <c r="S65" s="10" t="n">
+      <c r="S65" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="T65" s="10" t="n">
+      <c r="T65" s="11" t="n">
         <v>621</v>
       </c>
-      <c r="U65" s="10" t="inlineStr"/>
+      <c r="U65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -5641,12 +5657,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J66" s="7" t="inlineStr">
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5667,19 +5683,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O66" s="9" t="n"/>
-      <c r="P66" s="9" t="n"/>
-      <c r="Q66" s="9" t="n"/>
-      <c r="R66" s="10" t="n">
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="11" t="n">
         <v>1694</v>
       </c>
-      <c r="S66" s="10" t="n">
+      <c r="S66" s="11" t="n">
         <v>71</v>
       </c>
-      <c r="T66" s="10" t="n">
+      <c r="T66" s="11" t="n">
         <v>355</v>
       </c>
-      <c r="U66" s="10" t="inlineStr"/>
+      <c r="U66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -5712,12 +5728,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J67" s="7" t="inlineStr">
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5738,19 +5754,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O67" s="9" t="n"/>
-      <c r="P67" s="9" t="n"/>
-      <c r="Q67" s="9" t="n"/>
-      <c r="R67" s="10" t="n">
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="10" t="n"/>
+      <c r="Q67" s="10" t="n"/>
+      <c r="R67" s="11" t="n">
         <v>2027</v>
       </c>
-      <c r="S67" s="10" t="n">
+      <c r="S67" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="T67" s="10" t="n">
+      <c r="T67" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="U67" s="10" t="inlineStr"/>
+      <c r="U67" s="11" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -5783,12 +5799,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J68" s="7" t="inlineStr">
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5809,47 +5825,47 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O68" s="9" t="n"/>
-      <c r="P68" s="9" t="n"/>
-      <c r="Q68" s="9" t="n"/>
-      <c r="R68" s="10" t="n">
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="10" t="n"/>
+      <c r="Q68" s="10" t="n"/>
+      <c r="R68" s="11" t="n">
         <v>2486</v>
       </c>
-      <c r="S68" s="10" t="n">
+      <c r="S68" s="11" t="n">
         <v>378</v>
       </c>
-      <c r="T68" s="10" t="n">
+      <c r="T68" s="11" t="n">
         <v>537</v>
       </c>
-      <c r="U68" s="10" t="inlineStr"/>
+      <c r="U68" s="11" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="inlineStr">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>Stonor 3</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B69" s="13" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C69" s="14" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="D69" s="12" t="n">
+      <c r="D69" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="E69" s="14" t="n"/>
-      <c r="F69" s="14" t="n"/>
-      <c r="G69" s="14" t="n"/>
-      <c r="H69" s="14" t="n"/>
-      <c r="I69" s="14" t="n"/>
-      <c r="J69" s="14" t="n"/>
-      <c r="K69" s="14" t="n"/>
-      <c r="L69" s="14" t="n"/>
+      <c r="E69" s="15" t="n"/>
+      <c r="F69" s="15" t="n"/>
+      <c r="G69" s="15" t="n"/>
+      <c r="H69" s="15" t="n"/>
+      <c r="I69" s="15" t="n"/>
+      <c r="J69" s="15" t="n"/>
+      <c r="K69" s="15" t="n"/>
+      <c r="L69" s="15" t="n"/>
       <c r="M69" s="7" t="inlineStr">
         <is>
           <t>on file</t>
@@ -5863,16 +5879,16 @@
       <c r="O69" s="15" t="n"/>
       <c r="P69" s="15" t="n"/>
       <c r="Q69" s="15" t="n"/>
-      <c r="R69" s="10" t="n">
+      <c r="R69" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="S69" s="10" t="n">
+      <c r="S69" s="11" t="n">
         <v>141</v>
       </c>
-      <c r="T69" s="10" t="n">
+      <c r="T69" s="11" t="n">
         <v>121</v>
       </c>
-      <c r="U69" s="10" t="inlineStr"/>
+      <c r="U69" s="11" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -5905,12 +5921,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J70" s="7" t="inlineStr">
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -5931,16 +5947,16 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O70" s="9" t="n"/>
-      <c r="P70" s="9" t="n"/>
-      <c r="Q70" s="9" t="n"/>
-      <c r="R70" s="10" t="n">
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
+      <c r="Q70" s="10" t="n"/>
+      <c r="R70" s="11" t="n">
         <v>2147</v>
       </c>
-      <c r="S70" s="10" t="n">
+      <c r="S70" s="11" t="n">
         <v>155</v>
       </c>
-      <c r="T70" s="10" t="n">
+      <c r="T70" s="11" t="n">
         <v>248</v>
       </c>
       <c r="U70" s="8" t="inlineStr">
@@ -5984,12 +6000,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="inlineStr">
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6010,19 +6026,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O71" s="9" t="n"/>
-      <c r="P71" s="9" t="n"/>
-      <c r="Q71" s="9" t="n"/>
-      <c r="R71" s="10" t="n">
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="10" t="n"/>
+      <c r="Q71" s="10" t="n"/>
+      <c r="R71" s="11" t="n">
         <v>1650</v>
       </c>
-      <c r="S71" s="10" t="n">
+      <c r="S71" s="11" t="n">
         <v>256</v>
       </c>
-      <c r="T71" s="10" t="n">
+      <c r="T71" s="11" t="n">
         <v>253</v>
       </c>
-      <c r="U71" s="10" t="inlineStr"/>
+      <c r="U71" s="11" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6059,12 +6075,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J72" s="7" t="inlineStr">
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6085,16 +6101,16 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O72" s="9" t="n"/>
-      <c r="P72" s="9" t="n"/>
-      <c r="Q72" s="9" t="n"/>
-      <c r="R72" s="10" t="n">
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="11" t="n">
         <v>2295</v>
       </c>
-      <c r="S72" s="10" t="n">
+      <c r="S72" s="11" t="n">
         <v>215</v>
       </c>
-      <c r="T72" s="10" t="n">
+      <c r="T72" s="11" t="n">
         <v>251</v>
       </c>
       <c r="U72" s="8" t="inlineStr">
@@ -6130,12 +6146,12 @@
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J73" s="7" t="inlineStr">
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6152,19 +6168,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O73" s="9" t="n"/>
-      <c r="P73" s="9" t="n"/>
-      <c r="Q73" s="9" t="n"/>
-      <c r="R73" s="10" t="n">
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="10" t="n"/>
+      <c r="R73" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="S73" s="10" t="n">
+      <c r="S73" s="11" t="n">
         <v>248</v>
       </c>
-      <c r="T73" s="10" t="n">
+      <c r="T73" s="11" t="n">
         <v>526</v>
       </c>
-      <c r="U73" s="10" t="inlineStr"/>
+      <c r="U73" s="11" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -6197,12 +6213,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J74" s="7" t="inlineStr">
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6223,19 +6239,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O74" s="9" t="n"/>
-      <c r="P74" s="9" t="n"/>
-      <c r="Q74" s="9" t="n"/>
-      <c r="R74" s="10" t="n">
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="10" t="n"/>
+      <c r="Q74" s="10" t="n"/>
+      <c r="R74" s="11" t="n">
         <v>1937</v>
       </c>
-      <c r="S74" s="10" t="n">
+      <c r="S74" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="T74" s="10" t="n">
+      <c r="T74" s="11" t="n">
         <v>221</v>
       </c>
-      <c r="U74" s="10" t="inlineStr"/>
+      <c r="U74" s="11" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -6272,12 +6288,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="inlineStr">
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6298,19 +6314,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O75" s="9" t="n"/>
-      <c r="P75" s="9" t="n"/>
-      <c r="Q75" s="9" t="n"/>
-      <c r="R75" s="10" t="n">
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="10" t="n"/>
+      <c r="R75" s="11" t="n">
         <v>5212</v>
       </c>
-      <c r="S75" s="10" t="n">
+      <c r="S75" s="11" t="n">
         <v>177</v>
       </c>
-      <c r="T75" s="10" t="n">
+      <c r="T75" s="11" t="n">
         <v>303</v>
       </c>
-      <c r="U75" s="10" t="inlineStr"/>
+      <c r="U75" s="11" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -6339,12 +6355,12 @@
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J76" s="7" t="inlineStr">
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6361,19 +6377,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O76" s="9" t="n"/>
-      <c r="P76" s="9" t="n"/>
-      <c r="Q76" s="9" t="n"/>
-      <c r="R76" s="10" t="n">
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="10" t="n"/>
+      <c r="R76" s="11" t="n">
         <v>702</v>
       </c>
-      <c r="S76" s="10" t="n">
+      <c r="S76" s="11" t="n">
         <v>107</v>
       </c>
-      <c r="T76" s="10" t="n">
+      <c r="T76" s="11" t="n">
         <v>101</v>
       </c>
-      <c r="U76" s="10" t="inlineStr"/>
+      <c r="U76" s="11" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -6402,12 +6418,12 @@
       </c>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J77" s="7" t="inlineStr">
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6428,16 +6444,16 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O77" s="9" t="n"/>
-      <c r="P77" s="9" t="n"/>
-      <c r="Q77" s="9" t="n"/>
-      <c r="R77" s="10" t="n">
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="10" t="n"/>
+      <c r="Q77" s="10" t="n"/>
+      <c r="R77" s="11" t="n">
         <v>2142</v>
       </c>
-      <c r="S77" s="10" t="n">
+      <c r="S77" s="11" t="n">
         <v>129</v>
       </c>
-      <c r="T77" s="10" t="n">
+      <c r="T77" s="11" t="n">
         <v>207</v>
       </c>
       <c r="U77" s="8" t="inlineStr">
@@ -6481,12 +6497,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J78" s="7" t="inlineStr">
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6503,19 +6519,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O78" s="9" t="n"/>
-      <c r="P78" s="9" t="n"/>
-      <c r="Q78" s="9" t="n"/>
-      <c r="R78" s="10" t="n">
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="10" t="n"/>
+      <c r="R78" s="11" t="n">
         <v>2338</v>
       </c>
-      <c r="S78" s="10" t="n">
+      <c r="S78" s="11" t="n">
         <v>93</v>
       </c>
-      <c r="T78" s="10" t="n">
+      <c r="T78" s="11" t="n">
         <v>148</v>
       </c>
-      <c r="U78" s="10" t="inlineStr"/>
+      <c r="U78" s="11" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -6552,12 +6568,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J79" s="7" t="inlineStr">
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6578,19 +6594,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O79" s="9" t="n"/>
-      <c r="P79" s="9" t="n"/>
-      <c r="Q79" s="9" t="n"/>
-      <c r="R79" s="10" t="n">
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="10" t="n"/>
+      <c r="R79" s="11" t="n">
         <v>2399</v>
       </c>
-      <c r="S79" s="10" t="n">
+      <c r="S79" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="T79" s="10" t="n">
+      <c r="T79" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="U79" s="10" t="inlineStr"/>
+      <c r="U79" s="11" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -6627,12 +6643,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J80" s="7" t="inlineStr">
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6649,19 +6665,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O80" s="9" t="n"/>
-      <c r="P80" s="9" t="n"/>
-      <c r="Q80" s="9" t="n"/>
-      <c r="R80" s="10" t="n">
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="10" t="n"/>
+      <c r="Q80" s="10" t="n"/>
+      <c r="R80" s="11" t="n">
         <v>3998</v>
       </c>
-      <c r="S80" s="10" t="n">
+      <c r="S80" s="11" t="n">
         <v>146</v>
       </c>
-      <c r="T80" s="10" t="n">
+      <c r="T80" s="11" t="n">
         <v>329</v>
       </c>
-      <c r="U80" s="10" t="inlineStr"/>
+      <c r="U80" s="11" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -6690,12 +6706,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J81" s="7" t="inlineStr">
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6712,19 +6728,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O81" s="9" t="n"/>
-      <c r="P81" s="9" t="n"/>
-      <c r="Q81" s="9" t="n"/>
-      <c r="R81" s="10" t="n">
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="11" t="n">
         <v>1862</v>
       </c>
-      <c r="S81" s="10" t="n">
+      <c r="S81" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="T81" s="10" t="n">
+      <c r="T81" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="U81" s="10" t="inlineStr"/>
+      <c r="U81" s="11" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -6753,12 +6769,12 @@
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
       <c r="H82" s="8" t="n"/>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J82" s="7" t="inlineStr">
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6775,19 +6791,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O82" s="9" t="n"/>
-      <c r="P82" s="9" t="n"/>
-      <c r="Q82" s="9" t="n"/>
-      <c r="R82" s="10" t="n">
+      <c r="O82" s="10" t="n"/>
+      <c r="P82" s="10" t="n"/>
+      <c r="Q82" s="10" t="n"/>
+      <c r="R82" s="11" t="n">
         <v>572</v>
       </c>
-      <c r="S82" s="10" t="n">
+      <c r="S82" s="11" t="n">
         <v>98</v>
       </c>
-      <c r="T82" s="10" t="n">
+      <c r="T82" s="11" t="n">
         <v>176</v>
       </c>
-      <c r="U82" s="10" t="inlineStr"/>
+      <c r="U82" s="11" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -6824,12 +6840,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J83" s="7" t="inlineStr">
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6854,37 +6870,37 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O83" s="9" t="n"/>
-      <c r="P83" s="9" t="n"/>
-      <c r="Q83" s="9" t="n"/>
-      <c r="R83" s="10" t="n">
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="10" t="n"/>
+      <c r="R83" s="11" t="n">
         <v>2226</v>
       </c>
-      <c r="S83" s="10" t="n">
+      <c r="S83" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="T83" s="10" t="n">
+      <c r="T83" s="11" t="n">
         <v>99</v>
       </c>
-      <c r="U83" s="10" t="inlineStr"/>
+      <c r="U83" s="11" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="11" t="inlineStr">
+      <c r="A84" s="12" t="inlineStr">
         <is>
           <t>Tribeca Bukit Bintang</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="C84" s="13" t="inlineStr">
+      <c r="C84" s="14" t="inlineStr">
         <is>
           <t>SKIP</t>
         </is>
       </c>
-      <c r="D84" s="12" t="n">
+      <c r="D84" s="13" t="n">
         <v>7</v>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -6892,13 +6908,13 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="F84" s="14" t="n"/>
-      <c r="G84" s="14" t="n"/>
-      <c r="H84" s="14" t="n"/>
-      <c r="I84" s="14" t="n"/>
-      <c r="J84" s="14" t="n"/>
-      <c r="K84" s="14" t="n"/>
-      <c r="L84" s="14" t="n"/>
+      <c r="F84" s="15" t="n"/>
+      <c r="G84" s="15" t="n"/>
+      <c r="H84" s="15" t="n"/>
+      <c r="I84" s="15" t="n"/>
+      <c r="J84" s="15" t="n"/>
+      <c r="K84" s="15" t="n"/>
+      <c r="L84" s="15" t="n"/>
       <c r="M84" s="7" t="inlineStr">
         <is>
           <t>on file</t>
@@ -6912,16 +6928,16 @@
       <c r="O84" s="15" t="n"/>
       <c r="P84" s="15" t="n"/>
       <c r="Q84" s="15" t="n"/>
-      <c r="R84" s="10" t="n">
+      <c r="R84" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="S84" s="10" t="n">
+      <c r="S84" s="11" t="n">
         <v>160</v>
       </c>
-      <c r="T84" s="10" t="n">
+      <c r="T84" s="11" t="n">
         <v>117</v>
       </c>
-      <c r="U84" s="10" t="inlineStr"/>
+      <c r="U84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -6958,12 +6974,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J85" s="7" t="inlineStr">
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -6984,19 +7000,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O85" s="9" t="n"/>
-      <c r="P85" s="9" t="n"/>
-      <c r="Q85" s="9" t="n"/>
-      <c r="R85" s="10" t="n">
+      <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="10" t="n"/>
+      <c r="R85" s="11" t="n">
         <v>2566</v>
       </c>
-      <c r="S85" s="10" t="n">
+      <c r="S85" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="T85" s="10" t="n">
+      <c r="T85" s="11" t="n">
         <v>724</v>
       </c>
-      <c r="U85" s="10" t="inlineStr"/>
+      <c r="U85" s="11" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -7029,12 +7045,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J86" s="7" t="inlineStr">
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -7055,19 +7071,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O86" s="9" t="n"/>
-      <c r="P86" s="9" t="n"/>
-      <c r="Q86" s="9" t="n"/>
-      <c r="R86" s="10" t="n">
+      <c r="O86" s="10" t="n"/>
+      <c r="P86" s="10" t="n"/>
+      <c r="Q86" s="10" t="n"/>
+      <c r="R86" s="11" t="n">
         <v>2183</v>
       </c>
-      <c r="S86" s="10" t="n">
+      <c r="S86" s="11" t="n">
         <v>104</v>
       </c>
-      <c r="T86" s="10" t="n">
+      <c r="T86" s="11" t="n">
         <v>58</v>
       </c>
-      <c r="U86" s="10" t="inlineStr"/>
+      <c r="U86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -7104,12 +7120,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J87" s="7" t="inlineStr">
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -7130,19 +7146,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O87" s="9" t="n"/>
-      <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="9" t="n"/>
-      <c r="R87" s="10" t="n">
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="11" t="n">
         <v>1695</v>
       </c>
-      <c r="S87" s="10" t="n">
+      <c r="S87" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="T87" s="10" t="n">
+      <c r="T87" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="U87" s="10" t="inlineStr"/>
+      <c r="U87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -7179,12 +7195,12 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>on file</t>
-        </is>
-      </c>
-      <c r="J88" s="7" t="inlineStr">
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>on file</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="inlineStr">
         <is>
           <t>on file</t>
         </is>
@@ -7201,19 +7217,19 @@
           <t>on file</t>
         </is>
       </c>
-      <c r="O88" s="9" t="n"/>
-      <c r="P88" s="9" t="n"/>
-      <c r="Q88" s="9" t="n"/>
-      <c r="R88" s="10" t="n">
+      <c r="O88" s="10" t="n"/>
+      <c r="P88" s="10" t="n"/>
+      <c r="Q88" s="10" t="n"/>
+      <c r="R88" s="11" t="n">
         <v>981</v>
       </c>
-      <c r="S88" s="10" t="n">
+      <c r="S88" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="T88" s="10" t="n">
+      <c r="T88" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="U88" s="10" t="inlineStr"/>
+      <c r="U88" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:U88"/>
@@ -8228,18 +8244,18 @@
           <t>pricePsf</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>77.0%</t>
         </is>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="11" t="n">
         <v>63</v>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>75.9%</t>
         </is>
@@ -8261,18 +8277,18 @@
           <t>vpDate</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>73.6%</t>
         </is>
       </c>
-      <c r="D3" s="10" t="n">
+      <c r="D3" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>72.3%</t>
         </is>
@@ -8294,18 +8310,18 @@
           <t>unitTypes</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>42.5%</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>39.8%</t>
         </is>
@@ -8327,18 +8343,18 @@
           <t>bedrooms</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>37.9%</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>34.9%</t>
         </is>
@@ -8360,18 +8376,18 @@
           <t>priceValue</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>31.0%</t>
         </is>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>31.3%</t>
         </is>
@@ -8393,18 +8409,18 @@
           <t>size</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>23.0%</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>19.3%</t>
         </is>
@@ -8426,18 +8442,18 @@
           <t>tenure</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>4.6%</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -8459,18 +8475,18 @@
           <t>locationText</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>4.6%</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -8492,18 +8508,18 @@
           <t>collateral</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>1.1%</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>1.2%</t>
         </is>
@@ -8525,18 +8541,18 @@
           <t>description</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -8554,11 +8570,11 @@
     </row>
     <row r="12">
       <c r="A12" s="21" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
       <c r="G12" s="16" t="n"/>
     </row>
     <row r="13">
@@ -8567,11 +8583,11 @@
           <t>PRICE SIGNAL — what a client asking 'how much?' can actually be told</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
       <c r="G13" s="16" t="n"/>
     </row>
     <row r="14">
@@ -8580,23 +8596,23 @@
           <t>Total price stated</t>
         </is>
       </c>
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="11" t="n">
         <v>60</v>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>69.0%</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>68.7%</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr"/>
       <c r="G14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
@@ -8605,23 +8621,23 @@
           <t>psf rate only</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>23.0%</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>24.1%</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
       <c r="G15" s="16" t="inlineStr">
         <is>
           <t>Honest fallback — never multiply into a total.</t>
@@ -8634,23 +8650,23 @@
           <t>Per-layout prices only</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr"/>
+      <c r="F16" s="11" t="inlineStr"/>
       <c r="G16" s="16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -8659,18 +8675,18 @@
           <t>Nothing at all</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>8.0%</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>7.2%</t>
         </is>
